--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104712_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104712_W29.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5216</v>
+        <v>11.3968</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2852</v>
+        <v>9.8614</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2365</v>
+        <v>1.5354</v>
       </c>
       <c r="G2" t="n">
-        <v>9.638199999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5815</v>
+        <v>0.5828</v>
       </c>
       <c r="I2" t="n">
-        <v>9.056699999999999</v>
+        <v>9.0472</v>
       </c>
       <c r="J2" t="n">
-        <v>10.2598</v>
+        <v>10.2426</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1751</v>
+        <v>1.1721</v>
       </c>
       <c r="L2" t="n">
-        <v>9.0846</v>
+        <v>9.070499999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.6125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5936</v>
+        <v>-0.5893</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0279</v>
+        <v>-0.0232</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9069</v>
+        <v>0.7864</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1614</v>
+        <v>0.757</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2545</v>
+        <v>0.0294</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4703</v>
+        <v>3.0409</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8841</v>
+        <v>2.1543</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8989</v>
+        <v>3.8874</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6214</v>
+        <v>-1.6249</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5203</v>
+        <v>5.5124</v>
       </c>
       <c r="J3" t="n">
-        <v>5.084</v>
+        <v>5.0604</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1487</v>
+        <v>-0.1594</v>
       </c>
       <c r="L3" t="n">
-        <v>5.2327</v>
+        <v>5.2197</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1851</v>
+        <v>-1.1729</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4727</v>
+        <v>-1.4656</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2876</v>
+        <v>0.2926</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4752</v>
+        <v>0.1127</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2526</v>
+        <v>0.5571</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7278</v>
+        <v>-0.4444</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7266</v>
+        <v>1.7198</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0055</v>
+        <v>0.4114</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7211</v>
+        <v>1.3084</v>
       </c>
       <c r="G4" t="n">
-        <v>1.015</v>
+        <v>1.0181</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.4156</v>
+        <v>-2.4127</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4306</v>
+        <v>3.4308</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3024</v>
+        <v>2.2909</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8978</v>
+        <v>-0.9038</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2002</v>
+        <v>3.1947</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2874</v>
+        <v>-1.2728</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5178</v>
+        <v>-1.5089</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2304</v>
+        <v>0.2361</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0301</v>
+        <v>0.0188</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.025</v>
+        <v>0.3968</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0551</v>
+        <v>-0.378</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2257</v>
+        <v>1.2653</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0345</v>
+        <v>1.3828</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1913</v>
+        <v>-0.1175</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5306</v>
+        <v>0.4253</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4501</v>
+        <v>-0.1011</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0806</v>
+        <v>0.5264</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5013</v>
+        <v>2.2864</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3456</v>
+        <v>1.2066</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1557</v>
+        <v>1.0799</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0293</v>
+        <v>-1.8612</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1045</v>
+        <v>-1.3077</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0752</v>
+        <v>-0.5535</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6816</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4544</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6954</v>
+        <v>0.2058</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6691</v>
+        <v>0.2832</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0264</v>
+        <v>-0.0774</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3188</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9335</v>
+        <v>1.0009</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8516</v>
+        <v>0.6743</v>
       </c>
       <c r="F6" t="n">
-        <v>0.082</v>
+        <v>0.3266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4174</v>
+        <v>1.5324</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1052</v>
+        <v>1.4502</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5226</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2908</v>
+        <v>1.4991</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2097</v>
+        <v>0.3447</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0812</v>
+        <v>1.1543</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8735</v>
+        <v>0.0333</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3149</v>
+        <v>1.1055</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5585</v>
+        <v>-1.0722</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4544</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8175</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1207</v>
+        <v>0.467</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2587</v>
+        <v>0.3134</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1379</v>
+        <v>0.1535</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0913</v>
+        <v>-0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>J. KARNIK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.957</v>
+        <v>-0.2677</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1168</v>
+        <v>-1.933</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0737</v>
+        <v>1.6654</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3008</v>
+        <v>-0.2054</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0752</v>
+        <v>0.7179</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3761</v>
+        <v>-0.9233</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2748</v>
+        <v>-0.827</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3975</v>
+        <v>-0.1864</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8774</v>
+        <v>-0.6407</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.974</v>
+        <v>0.6217</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4727</v>
+        <v>0.9043</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5013</v>
+        <v>-0.2826</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0447</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1965</v>
+        <v>-0.202</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2497</v>
+        <v>0.0322</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0532</v>
+        <v>-0.2342</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0913</v>
+        <v>-0.3155</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0913</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. KARNIK</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0474</v>
+        <v>-1.4143</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6349</v>
+        <v>-0.4229</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5875</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2085</v>
+        <v>0.3023</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7175</v>
+        <v>-1.0691</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.926</v>
+        <v>1.3714</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8238</v>
+        <v>2.2649</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1841</v>
+        <v>0.3964</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6398</v>
+        <v>1.8684</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6153</v>
+        <v>-1.9626</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9016</v>
+        <v>-1.4656</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2863</v>
+        <v>-0.497</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4544</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5903</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9744</v>
+        <v>0.7387</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6751</v>
+        <v>0.7268</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2993</v>
+        <v>0.0119</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3188</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2894</v>
+        <v>-1.6342</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2248</v>
+        <v>-1.7119</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0646</v>
+        <v>0.0776</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2233</v>
+        <v>0.2264</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5988</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3755</v>
+        <v>-0.3737</v>
       </c>
       <c r="J9" t="n">
-        <v>0.056</v>
+        <v>0.0492</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4035</v>
+        <v>0.3997</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3475</v>
+        <v>-0.3505</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1674</v>
+        <v>0.1771</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1953</v>
+        <v>0.2003</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0279</v>
+        <v>-0.0232</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.26</v>
+        <v>-0.0882</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9911</v>
+        <v>0.5152</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.731</v>
+        <v>-0.6034</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0928</v>
+        <v>-1.8442</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4949</v>
+        <v>-1.0004</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4021</v>
+        <v>-0.8437</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6875</v>
+        <v>1.4274</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1406</v>
+        <v>2.9438</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8281</v>
+        <v>-1.5164</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6144</v>
+        <v>1.5083</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.8961</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6956</v>
+        <v>-0.3877</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.073</v>
+        <v>-0.081</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0594</v>
+        <v>1.0477</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1324</v>
+        <v>-1.1287</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3631</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9578</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3914</v>
+        <v>-0.1838</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5664</v>
+        <v>-0.5838</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.349</v>
+        <v>-2.7697</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3367</v>
+        <v>-3.7465</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0123</v>
+        <v>0.9768</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4281</v>
+        <v>-1.6897</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9453</v>
+        <v>1.1376</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5172</v>
+        <v>-2.8274</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5161</v>
+        <v>-1.6232</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9009</v>
+        <v>0.0755</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3848</v>
+        <v>-1.6987</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0881</v>
+        <v>-0.0665</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0443</v>
+        <v>1.0622</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1324</v>
+        <v>-1.1287</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4991</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4078</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.278</v>
+        <v>0.2859</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5363</v>
+        <v>0.1531</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7417</v>
+        <v>0.1328</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.1421</v>
+        <v>10.4936</v>
       </c>
       <c r="E12" t="n">
-        <v>5.486399999999998</v>
+        <v>5.6695</v>
       </c>
       <c r="F12" t="n">
-        <v>4.6561</v>
+        <v>4.8242</v>
       </c>
       <c r="G12" t="n">
-        <v>16.5563</v>
+        <v>16.5542</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2164</v>
+        <v>2.224499999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>14.3401</v>
+        <v>14.3295</v>
       </c>
       <c r="J12" t="n">
-        <v>22.847</v>
+        <v>22.7516</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2829</v>
+        <v>4.241499999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>18.5641</v>
+        <v>18.5099</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.2906</v>
+        <v>-6.1974</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0666</v>
+        <v>-2.017100000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.2239</v>
+        <v>-4.180400000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.8157</v>
+        <v>-6.828899999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-23.8546</v>
+        <v>-23.9014</v>
       </c>
       <c r="R12" t="n">
-        <v>17.039</v>
+        <v>17.0723</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1984</v>
+        <v>1.5575</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2202</v>
+        <v>3.551</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0217</v>
+        <v>-1.9936</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7969999999999999</v>
+        <v>-0.7887999999999997</v>
       </c>
       <c r="W12" t="n">
-        <v>3.2739</v>
+        <v>3.2685</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.0709</v>
+        <v>-4.0573</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3241</v>
+        <v>3.6086</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6447</v>
+        <v>3.4979</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3206</v>
+        <v>0.1106</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4518</v>
+        <v>1.4465</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7581</v>
+        <v>0.7556</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6937</v>
+        <v>0.6909</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5704</v>
+        <v>4.551</v>
       </c>
       <c r="K13" t="n">
-        <v>1.239</v>
+        <v>1.2303</v>
       </c>
       <c r="L13" t="n">
-        <v>3.3313</v>
+        <v>3.3206</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1186</v>
+        <v>-3.1045</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4809</v>
+        <v>-0.4747</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6376</v>
+        <v>-2.6298</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>3.635</v>
+        <v>3.6421</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3498</v>
+        <v>0.6385</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1868</v>
+        <v>1.0655</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.837</v>
+        <v>-0.427</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1268</v>
+        <v>2.6015</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5342</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5926</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1541</v>
+        <v>-2.1544</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1322</v>
+        <v>-0.1346</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.0218</v>
+        <v>-2.0198</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4339</v>
+        <v>0.4198</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1909</v>
+        <v>0.1821</v>
       </c>
       <c r="L14" t="n">
-        <v>0.243</v>
+        <v>0.2377</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.588</v>
+        <v>-2.5742</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3231</v>
+        <v>-0.3168</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2648</v>
+        <v>-2.2574</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>4.0894</v>
+        <v>4.0974</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2809</v>
+        <v>0.7559</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1897</v>
+        <v>0.659</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0912</v>
+        <v>0.0969</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.107</v>
+        <v>1.6992</v>
       </c>
       <c r="E15" t="n">
-        <v>1.171</v>
+        <v>0.6956</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9361</v>
+        <v>1.0036</v>
       </c>
       <c r="G15" t="n">
         <v>0.8758</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3652</v>
+        <v>0.3648</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.511</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5903</v>
+        <v>0.5888</v>
       </c>
       <c r="K15" t="n">
-        <v>0.553</v>
+        <v>0.5516</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2855</v>
+        <v>0.287</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4733</v>
+        <v>0.4738</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5497</v>
+        <v>0.1405</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5807</v>
+        <v>0.1067</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.031</v>
+        <v>0.0338</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.223</v>
+        <v>0.445</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0039</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7809</v>
+        <v>1.1431</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2545</v>
+        <v>-2.0508</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1939</v>
+        <v>-0.546</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0606</v>
+        <v>-1.5048</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4111</v>
+        <v>-0.2053</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.909</v>
+        <v>-0.1002</v>
       </c>
       <c r="L16" t="n">
-        <v>0.498</v>
+        <v>-0.1051</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8434</v>
+        <v>-1.8455</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2848</v>
+        <v>-0.4458</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5585</v>
+        <v>-1.3997</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1359</v>
+        <v>2.7316</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4991</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>3.635</v>
+        <v>2.9592</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9868</v>
+        <v>-0.2358</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9063</v>
+        <v>-0.2652</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0805</v>
+        <v>0.0294</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3018</v>
+        <v>-0.233</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3951</v>
+        <v>-0.057</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0933</v>
+        <v>-0.176</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0517</v>
+        <v>-0.0413</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5485</v>
+        <v>0.1924</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5032</v>
+        <v>-0.2337</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1962</v>
+        <v>0.5888</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0977</v>
+        <v>0.5516</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0985</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8555</v>
+        <v>-0.6301</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4508</v>
+        <v>-0.3592</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4047</v>
+        <v>-0.271</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7262</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9534</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.4193</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9717</v>
+        <v>-0.4182</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0046</v>
+        <v>-0.0011</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3272</v>
+        <v>-1.2169</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0533</v>
+        <v>-2.2116</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2739</v>
+        <v>0.9948</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0427</v>
+        <v>-2.2594</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1923</v>
+        <v>-2.1966</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.235</v>
+        <v>-0.0629</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5903</v>
+        <v>-0.4271</v>
       </c>
       <c r="K18" t="n">
-        <v>0.553</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.4906</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6329</v>
+        <v>-1.8323</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3607</v>
+        <v>-1.2788</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2723</v>
+        <v>-0.5535</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2272</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2272</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4544</v>
+        <v>3.6421</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5118</v>
+        <v>0.9939</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4164</v>
+        <v>0.7195</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0953</v>
+        <v>0.2744</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6787</v>
+        <v>-1.5499</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2474</v>
+        <v>0.2392</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9261</v>
+        <v>-1.7891</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5666</v>
+        <v>-0.5661</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.8358</v>
       </c>
       <c r="I19" t="n">
         <v>0.2696</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0993</v>
+        <v>1.0941</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4606</v>
+        <v>-0.4621</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5598</v>
+        <v>1.5563</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6659</v>
+        <v>-1.6603</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3757</v>
+        <v>-0.3736</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2902</v>
+        <v>-1.2866</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9296</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6247</v>
+        <v>-0.6273</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3049</v>
+        <v>-0.1775</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,37 +1969,37 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4837</v>
+        <v>-2.4827</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.874</v>
+        <v>-0.8761</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6097</v>
+        <v>-1.6066</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4812</v>
+        <v>-0.4799</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5184</v>
+        <v>-0.5171</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5184</v>
+        <v>-0.5171</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5184</v>
+        <v>-0.5171</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2014,28 +2014,28 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8637</v>
+        <v>-1.8634</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9393</v>
+        <v>-3.2554</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0912</v>
+        <v>0.3656</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8482</v>
+        <v>-3.621</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.9709</v>
+        <v>-1.6201</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3607</v>
+        <v>2.8637</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6103</v>
+        <v>-4.4838</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5848</v>
+        <v>3.2043</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6161</v>
+        <v>3.3095</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0313</v>
+        <v>-0.1051</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3861</v>
+        <v>-4.8244</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2554</v>
+        <v>-0.4458</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.6416</v>
+        <v>-4.3786</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9087</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4078</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4991</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7809</v>
+        <v>-1.1313</v>
       </c>
       <c r="T21" t="n">
-        <v>1.742</v>
+        <v>-0.2861</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0389</v>
+        <v>-0.8452</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4816</v>
+        <v>-3.6734</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4348</v>
+        <v>-2.8135</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.0468</v>
+        <v>-0.8599</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6186</v>
+        <v>-3.9635</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8672</v>
+        <v>-0.3592</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.4857</v>
+        <v>-3.6043</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2195</v>
+        <v>-0.5877</v>
       </c>
       <c r="K22" t="n">
-        <v>3.318</v>
+        <v>-0.6173</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0985</v>
+        <v>0.0296</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.838</v>
+        <v>-3.3758</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4508</v>
+        <v>0.2581</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.3872</v>
+        <v>-3.6339</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5903</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.635</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0447</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.364</v>
+        <v>1.0429</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1105</v>
+        <v>1.0309</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2534</v>
+        <v>0.0119</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0913</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0913</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2648</v>
+        <v>-4.5089</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4009</v>
+        <v>-3.9474</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8639</v>
+        <v>-0.5615</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.7437</v>
+        <v>-5.7409</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8092</v>
+        <v>-1.8118</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.9345</v>
+        <v>-3.9291</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0581</v>
+        <v>-3.0665</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.704</v>
+        <v>-1.7107</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3541</v>
+        <v>-1.3559</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6856</v>
+        <v>-2.6744</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1052</v>
+        <v>-0.1011</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5804</v>
+        <v>-2.5733</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2262</v>
+        <v>-0.4705</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3216</v>
+        <v>0.1482</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9046</v>
+        <v>-0.6187</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.1422</v>
+        <v>-8.565899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6559</v>
+        <v>-4.824</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.486300000000001</v>
+        <v>-3.742</v>
       </c>
       <c r="G24" t="n">
-        <v>-16.5564</v>
+        <v>-16.5541</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.2163</v>
+        <v>-2.2246</v>
       </c>
       <c r="I24" t="n">
-        <v>-14.3399</v>
+        <v>-14.3297</v>
       </c>
       <c r="J24" t="n">
-        <v>6.290800000000001</v>
+        <v>6.197400000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0665</v>
+        <v>2.016999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>4.224200000000001</v>
+        <v>4.1803</v>
       </c>
       <c r="M24" t="n">
-        <v>-22.8469</v>
+        <v>-22.7516</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.2828</v>
+        <v>-4.2416</v>
       </c>
       <c r="O24" t="n">
-        <v>-18.564</v>
+        <v>-18.51</v>
       </c>
       <c r="P24" t="n">
-        <v>6.815599999999999</v>
+        <v>6.829100000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0392</v>
+        <v>-17.0722</v>
       </c>
       <c r="R24" t="n">
-        <v>23.85469999999999</v>
+        <v>23.9014</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1986</v>
+        <v>0.3705000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0218</v>
+        <v>1.9936</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2202</v>
+        <v>-1.6231</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7969999999999997</v>
+        <v>0.7888000000000002</v>
       </c>
       <c r="W24" t="n">
-        <v>4.0709</v>
+        <v>4.0573</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.2739</v>
+        <v>-3.2685</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104712_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104712_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-4.0573</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104712_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-3.2685</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
